--- a/Mediciones/RNA/T/RUN3_T_2NO.xlsx
+++ b/Mediciones/RNA/T/RUN3_T_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA44E39-F0BF-4FF0-9CB1-BD44331B78FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE110AC6-F900-4723-AA78-C7FCF99B0600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -474,6 +474,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:15:44",
   "bounds": {
@@ -484,7 +487,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -575,9 +578,6 @@
   "run_id": "R20260718_221544",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -933,7 +933,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2">
         <v>1.7726943577837679E-2</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3">
         <v>1.7726943577837679E-2</v>
@@ -1146,7 +1146,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4">
         <v>1.7726943577837679E-2</v>
@@ -1200,7 +1200,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5">
         <v>1.7726943577837679E-2</v>
@@ -1254,7 +1254,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D6">
         <v>1.7726943577837679E-2</v>
@@ -1308,7 +1308,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7">
         <v>1.7726943577837679E-2</v>
@@ -1362,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8">
         <v>1.7726943577837679E-2</v>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D9">
         <v>1.7726943577837679E-2</v>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>1.7726943577837679E-2</v>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11">
         <v>1.7726943577837679E-2</v>
@@ -1578,7 +1578,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D12">
         <v>1.7726943577837679E-2</v>
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13">
         <v>1.7726943577837679E-2</v>
@@ -1686,7 +1686,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D14">
         <v>1.7726943577837679E-2</v>
@@ -1740,7 +1740,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D15">
         <v>1.7726943577837679E-2</v>
@@ -1794,7 +1794,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D16">
         <v>1.802987412591732E-2</v>
@@ -1848,7 +1848,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D17">
         <v>1.802987412591732E-2</v>
@@ -1902,7 +1902,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D18">
         <v>1.8229070090900901E-2</v>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D19">
         <v>1.8229070090900901E-2</v>
@@ -2010,7 +2010,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20">
         <v>1.8229070090900901E-2</v>
@@ -2064,7 +2064,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21">
         <v>2.1294401140026849E-2</v>
@@ -2118,7 +2118,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D22">
         <v>2.1294401140026849E-2</v>
@@ -2172,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D23">
         <v>2.1294401140026849E-2</v>
@@ -2226,7 +2226,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D24">
         <v>5.9345593932614439E-2</v>
@@ -2280,7 +2280,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25">
         <v>0.49237014339663082</v>
@@ -2334,7 +2334,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D26">
         <v>0.68508193349897395</v>
@@ -2388,7 +2388,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D27">
         <v>0.81911694950978098</v>
@@ -2442,7 +2442,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D28">
         <v>0.81911694950978098</v>
@@ -2496,7 +2496,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29">
         <v>0.81911694950978098</v>
@@ -2550,7 +2550,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D30">
         <v>0.81911694950978098</v>
@@ -2604,7 +2604,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31">
         <v>0.96244521683936912</v>
@@ -2658,7 +2658,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32">
         <v>0.96244521683936912</v>
@@ -2712,7 +2712,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D33">
         <v>0.96244521683936912</v>
@@ -2766,7 +2766,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D34">
         <v>0.96244521683936912</v>
@@ -2820,7 +2820,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D35">
         <v>0.96244521683936912</v>
@@ -2874,7 +2874,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36">
         <v>0.96244521683936912</v>
@@ -2928,7 +2928,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D37">
         <v>0.96244521683936912</v>
@@ -2982,7 +2982,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D38">
         <v>0.96244521683936912</v>
@@ -3036,7 +3036,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D39">
         <v>0.96244521683936912</v>
@@ -3090,7 +3090,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40">
         <v>0.96244521683936912</v>
@@ -3144,7 +3144,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D41">
         <v>0.96244521683936912</v>
@@ -3198,7 +3198,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D42">
         <v>0.96244521683936912</v>
@@ -3252,7 +3252,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D43">
         <v>0.96244521683936912</v>
@@ -3306,7 +3306,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D44">
         <v>0.96244521683936912</v>
@@ -3360,7 +3360,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D45">
         <v>0.96244521683936912</v>
@@ -3414,7 +3414,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D46">
         <v>0.96244521683936912</v>
@@ -3468,7 +3468,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D47">
         <v>0.96244521683936912</v>
@@ -3522,7 +3522,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D48">
         <v>0.96244521683936912</v>
@@ -3576,7 +3576,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D49">
         <v>0.96244521683936912</v>
@@ -3630,7 +3630,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D50">
         <v>0.96244521683936912</v>
@@ -3684,7 +3684,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D51">
         <v>0.96244521683936912</v>
@@ -3738,7 +3738,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D52">
         <v>0.96244521683936912</v>
@@ -3792,7 +3792,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D53">
         <v>0.96244521683936912</v>
@@ -3846,7 +3846,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D54">
         <v>0.96244521683936912</v>
@@ -3900,7 +3900,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D55">
         <v>0.96244521683936912</v>
@@ -3954,7 +3954,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D56">
         <v>0.96244521683936912</v>
@@ -4008,7 +4008,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D57">
         <v>0.96244521683936912</v>
@@ -4062,7 +4062,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D58">
         <v>0.96244521683936912</v>
@@ -4116,7 +4116,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D59">
         <v>0.96244521683936912</v>
@@ -4170,7 +4170,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D60">
         <v>0.99144054005466686</v>
@@ -4224,7 +4224,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D61">
         <v>0.99144054005466686</v>
@@ -4278,7 +4278,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D62">
         <v>0.99144054005466686</v>
@@ -4332,7 +4332,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D63">
         <v>0.99144054005466686</v>
@@ -4386,7 +4386,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D64">
         <v>0.99144054005466686</v>
@@ -4440,7 +4440,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D65">
         <v>0.99144054005466686</v>
@@ -4494,7 +4494,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D66">
         <v>0.99144054005466686</v>
@@ -4548,7 +4548,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D67">
         <v>0.99144054005466686</v>
@@ -4602,7 +4602,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D68">
         <v>0.99144054005466686</v>
@@ -4656,7 +4656,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D69">
         <v>0.99144054005466686</v>
@@ -4710,7 +4710,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D70">
         <v>0.99144054005466686</v>
@@ -4764,7 +4764,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D71">
         <v>0.99144054005466686</v>
@@ -4818,7 +4818,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D72">
         <v>0.99144054005466686</v>
@@ -4872,7 +4872,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D73">
         <v>0.99144054005466686</v>
@@ -4926,7 +4926,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D74">
         <v>0.99144054005466686</v>
@@ -4980,7 +4980,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D75">
         <v>0.99144054005466686</v>
@@ -5034,7 +5034,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D76">
         <v>0.99144054005466686</v>
@@ -5088,7 +5088,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D77">
         <v>0.99144054005466686</v>
@@ -5142,7 +5142,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D78">
         <v>0.99144054005466686</v>
@@ -5196,7 +5196,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D79">
         <v>0.99144054005466686</v>
@@ -5250,7 +5250,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D80">
         <v>0.99144054005466686</v>
@@ -5304,7 +5304,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D81">
         <v>0.99144054005466686</v>
@@ -5358,7 +5358,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D82">
         <v>0.99144054005466686</v>
@@ -5412,7 +5412,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D83">
         <v>0.99144054005466686</v>
@@ -5466,7 +5466,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D84">
         <v>0.99144054005466686</v>
@@ -5520,7 +5520,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D85">
         <v>0.99144054005466686</v>
@@ -5574,7 +5574,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D86">
         <v>0.99144054005466686</v>
@@ -5628,7 +5628,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D87">
         <v>0.99144054005466686</v>
@@ -5682,7 +5682,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D88">
         <v>0.99144054005466686</v>
@@ -5736,7 +5736,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D89">
         <v>0.99144054005466686</v>
@@ -5790,7 +5790,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D90">
         <v>0.99144054005466686</v>
@@ -5844,7 +5844,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D91">
         <v>0.99144054005466686</v>
@@ -5898,7 +5898,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D92">
         <v>0.99144054005466686</v>
@@ -5952,7 +5952,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D93">
         <v>0.99144054005466686</v>
@@ -6006,7 +6006,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D94">
         <v>0.99144054005466686</v>
@@ -6060,7 +6060,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D95">
         <v>0.99144054005466686</v>
@@ -6114,7 +6114,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D96">
         <v>0.99144054005466686</v>
@@ -6168,7 +6168,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D97">
         <v>0.99144054005466686</v>
@@ -6222,7 +6222,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D98">
         <v>0.99144054005466686</v>
@@ -6276,7 +6276,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D99">
         <v>0.99144054005466686</v>
@@ -6330,7 +6330,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D100">
         <v>0.99144054005466686</v>
@@ -6384,7 +6384,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D101">
         <v>0.99144054005466686</v>
@@ -6438,7 +6438,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D102">
         <v>0.99144054005466686</v>
@@ -6492,7 +6492,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D103">
         <v>0.99144054005466686</v>
@@ -6546,7 +6546,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D104">
         <v>0.99144054005466686</v>
@@ -6600,7 +6600,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D105">
         <v>0.99144054005466686</v>
@@ -6654,7 +6654,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D106">
         <v>0.99144054005466686</v>
@@ -6708,7 +6708,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D107">
         <v>0.99144054005466686</v>
@@ -6762,7 +6762,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D108">
         <v>0.99144054005466686</v>
@@ -6816,7 +6816,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D109">
         <v>0.99144054005466686</v>
@@ -6870,7 +6870,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D110">
         <v>0.99144054005466686</v>
@@ -6924,7 +6924,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D111">
         <v>0.99144054005466686</v>
@@ -6978,7 +6978,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D112">
         <v>0.99144054005466686</v>
@@ -7032,7 +7032,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D113">
         <v>0.99144054005466686</v>
@@ -7086,7 +7086,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D114">
         <v>0.99144054005466686</v>
@@ -7140,7 +7140,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D115">
         <v>0.99144054005466686</v>
@@ -7194,7 +7194,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D116">
         <v>0.99144054005466686</v>
@@ -7248,7 +7248,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D117">
         <v>0.99144054005466686</v>
@@ -7302,7 +7302,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D118">
         <v>0.99144054005466686</v>
@@ -7356,7 +7356,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D119">
         <v>0.99144054005466686</v>
@@ -7410,7 +7410,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D120">
         <v>0.99144054005466686</v>
@@ -7464,7 +7464,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D121">
         <v>0.99144054005466686</v>
@@ -13681,7 +13681,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
